--- a/backtest_runs/20260410_193731/by_symbol/SUTM/SUTM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SUTM/SUTM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-3375.180000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>96624.81999999999</v>
@@ -1047,7 +1047,7 @@
         <v>-7500.399999999997</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>106154.74</v>
@@ -1139,7 +1139,7 @@
         <v>-2470.72000000001</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>111570.47</v>
@@ -1231,7 +1231,7 @@
         <v>-7919.540000000007</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>106077.53</v>
@@ -1277,7 +1277,7 @@
         <v>-9927</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>96150.53</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>96150.53</v>
@@ -1642,10 +1642,10 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>99062.45</v>
